--- a/data/merged/2026-08-31/MERGED_FR_Spot-Cleaner_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_FR_Spot-Cleaner_2026-08-31.xlsx
@@ -3427,13 +3427,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3471,13 +3471,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3521,7 +3521,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3565,7 +3565,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3691,13 +3691,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3735,13 +3735,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3999,13 +3999,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4043,13 +4043,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4131,13 +4131,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4175,13 +4175,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4263,13 +4263,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4307,13 +4307,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4351,13 +4351,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4395,13 +4395,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4571,13 +4571,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4615,7 +4615,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4665,7 +4665,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4703,13 +4703,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4791,13 +4791,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4885,7 +4885,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4929,7 +4929,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5099,13 +5099,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5143,13 +5143,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5451,13 +5451,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5474,50 +5474,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5859,7 +5815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6486,7 +6442,7 @@
       <c r="B4" s="13"/>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B07GXS35PG</t>
         </is>
       </c>
       <c r="D4" s="14"/>
@@ -6499,23 +6455,23 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>Bissell Brosse pour Taches Tenaces, Noir, 15 cm</t>
+          <t>BISSELL SpotClean ProHeat Shampouineuse Canapé 330W 36988sDesign compact, technologie HeatWave, pour tapis, moquettes, meub</t>
         </is>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B07999DC2C?psc=1</t>
+          <t>https://www.amazon.fr/dp/B07GXS35PG?psc=1</t>
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61aI3+gXJwL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/712YG8KRpfL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B07GXS35PG</t>
         </is>
       </c>
       <c r="M4" s="1"/>
@@ -6532,17 +6488,17 @@
       <c r="X4" s="15"/>
       <c r="Y4"/>
       <c r="Z4" s="19">
-        <v>20.82</v>
+        <v>108.32</v>
       </c>
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
       <c r="AD4" s="20">
-        <v>1376</v>
+        <v>24052</v>
       </c>
       <c r="AE4"/>
       <c r="AF4" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG4" s="22">
         <v>0</v>
@@ -6594,7 +6550,7 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B07GXS35PG</t>
+          <t>B07NH2DYTN</t>
         </is>
       </c>
       <c r="D5" s="14"/>
@@ -6607,23 +6563,23 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean ProHeat Shampouineuse Canapé 330W 36988sDesign compact, technologie HeatWave, pour tapis, moquettes, meub</t>
+          <t>BISSELL Spot &amp; Stain Pet Produit Nettoyant 1085NsContre les odeurs et taches d'animaux, compatible avec tous les détachants</t>
         </is>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B07GXS35PG?psc=1</t>
+          <t>https://www.amazon.fr/dp/B07NH2DYTN?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/712YG8KRpfL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61uBPKfdYRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B07GXS35PG</t>
+          <t>B07NH2DYTN</t>
         </is>
       </c>
       <c r="M5" s="1"/>
@@ -6639,18 +6595,16 @@
       <c r="W5" s="15"/>
       <c r="X5" s="15"/>
       <c r="Y5"/>
-      <c r="Z5" s="19">
-        <v>108.32</v>
-      </c>
+      <c r="Z5" s="19"/>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5"/>
       <c r="AD5" s="20">
-        <v>24052</v>
+        <v>8986</v>
       </c>
       <c r="AE5"/>
       <c r="AF5" s="21">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AG5" s="22">
         <v>0</v>
@@ -6702,7 +6656,7 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B07NH2DYTN</t>
+          <t>B084PSXMQM</t>
         </is>
       </c>
       <c r="D6" s="14"/>
@@ -6715,23 +6669,23 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Spot &amp; Stain Pet Produit Nettoyant 1085NsContre les odeurs et taches d'animaux, compatible avec tous les détachants</t>
+          <t>BISSELL SpotClean Pet Pro Shampouineuse Canapé 750W 15585sIdéal pour les propriétaires d'animaux, nettoyeur pour tapis, moq</t>
         </is>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B07NH2DYTN?psc=1</t>
+          <t>https://www.amazon.fr/dp/B084PSXMQM?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61uBPKfdYRL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/717n80vcVUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B07NH2DYTN</t>
+          <t>B084PSXMQM</t>
         </is>
       </c>
       <c r="M6" s="1"/>
@@ -6747,16 +6701,18 @@
       <c r="W6" s="15"/>
       <c r="X6" s="15"/>
       <c r="Y6"/>
-      <c r="Z6" s="19"/>
+      <c r="Z6" s="19">
+        <v>166.66</v>
+      </c>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6"/>
       <c r="AD6" s="20">
-        <v>8986</v>
+        <v>21173</v>
       </c>
       <c r="AE6"/>
       <c r="AF6" s="21">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AG6" s="22">
         <v>0</v>
@@ -6808,7 +6764,7 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B084PSXMQM</t>
+          <t>B08DG69QHL</t>
         </is>
       </c>
       <c r="D7" s="14"/>
@@ -6821,23 +6777,23 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean Pet Pro Shampouineuse Canapé 750W 15585sIdéal pour les propriétaires d'animaux, nettoyeur pour tapis, moq</t>
+          <t>TAPIS ET MOQUETTES VORWERK KOBOSAN LEPRECHAUN</t>
         </is>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B084PSXMQM?psc=1</t>
+          <t>https://www.amazon.fr/dp/B08DG69QHL?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/717n80vcVUL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41HEOK25hnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B084PSXMQM</t>
+          <t>B08DG69QHL</t>
         </is>
       </c>
       <c r="M7" s="1"/>
@@ -6853,18 +6809,16 @@
       <c r="W7" s="15"/>
       <c r="X7" s="15"/>
       <c r="Y7"/>
-      <c r="Z7" s="19">
-        <v>166.66</v>
-      </c>
+      <c r="Z7" s="19"/>
       <c r="AA7"/>
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7" s="20">
-        <v>21173</v>
+        <v>7</v>
       </c>
       <c r="AE7"/>
       <c r="AF7" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG7" s="22">
         <v>0</v>
@@ -6916,7 +6870,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B08DG69QHL</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="D8" s="14"/>
@@ -6929,23 +6883,23 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>TAPIS ET MOQUETTES VORWERK KOBOSAN LEPRECHAUN</t>
+          <t>MEDION Nettoyeur de tissus injecteur extracteur (Aspirateur eau pour tissus, moquettes et sièges auto, réservoir d'eau propre</t>
         </is>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B08DG69QHL?psc=1</t>
+          <t>https://www.amazon.fr/dp/B08KXVXC82?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41HEOK25hnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B08DG69QHL</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="M8" s="1"/>
@@ -6966,7 +6920,7 @@
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8" s="20">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="AE8"/>
       <c r="AF8" s="21">
@@ -7022,7 +6976,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="D9" s="14"/>
@@ -7035,23 +6989,23 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>MEDION Nettoyeur de tissus injecteur extracteur (Aspirateur eau pour tissus, moquettes et sièges auto, réservoir d'eau propre</t>
+          <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double RéservoirsNettoyeur de Tapis, Réservoirs 1,1 L + 0,5 L, Tuyau 1,2 m, 2</t>
         </is>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B08KXVXC82?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="M9" s="1"/>
@@ -7072,11 +7026,11 @@
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9" s="20">
-        <v>69</v>
+        <v>4805</v>
       </c>
       <c r="AE9"/>
       <c r="AF9" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG9" s="22">
         <v>0</v>
@@ -7128,7 +7082,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0BMF3LFC8</t>
         </is>
       </c>
       <c r="D10" s="14"/>
@@ -7141,23 +7095,23 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double RéservoirsNettoyeur de Tapis, Réservoirs 1,1 L + 0,5 L, Tuyau 1,2 m, 2</t>
+          <t>Vacmaster SCA0801 Aspirateur Nettoyeur de Tapis pour canapé, Tapis, Rembourrage, VoituresAspirateur Eau-Sec Forte Aspiratio</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0BMF3LFC8?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0BMF3LFC8</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -7173,16 +7127,18 @@
       <c r="W10" s="15"/>
       <c r="X10" s="15"/>
       <c r="Y10"/>
-      <c r="Z10" s="19"/>
+      <c r="Z10" s="19">
+        <v>82.5</v>
+      </c>
       <c r="AA10"/>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="20">
-        <v>4805</v>
+        <v>3805</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG10" s="22">
         <v>0</v>
@@ -7234,7 +7190,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0BMF3LFC8</t>
+          <t>B0BS13X4Z2</t>
         </is>
       </c>
       <c r="D11" s="14"/>
@@ -7247,23 +7203,23 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster SCA0801 Aspirateur Nettoyeur de Tapis pour canapé, Tapis, Rembourrage, VoituresAspirateur Eau-Sec Forte Aspiratio</t>
+          <t>Kärcher Injecteur-extracteur Puzzi 8/1, pour tissus d'ameublement et surfaces textiles, réservoir d'eau : 8 l, rendement de s</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0BMF3LFC8?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0BS13X4Z2?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71o8bjO+qpL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0BMF3LFC8</t>
+          <t>B0BS13X4Z2</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -7279,18 +7235,16 @@
       <c r="W11" s="15"/>
       <c r="X11" s="15"/>
       <c r="Y11"/>
-      <c r="Z11" s="19">
-        <v>82.5</v>
-      </c>
+      <c r="Z11" s="19"/>
       <c r="AA11"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="20">
-        <v>3805</v>
+        <v>1116</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG11" s="22">
         <v>0</v>
@@ -7342,7 +7296,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0BS13X4Z2</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -7355,23 +7309,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Kärcher Injecteur-extracteur Puzzi 8/1, pour tissus d'ameublement et surfaces textiles, réservoir d'eau : 8 l, rendement de s</t>
+          <t>H.Koenig Nettoyeur Détacheur TWT77, Shampouineuse, Nettoyeur Tapis Canapé et Tissu, Double Réservoir, Brosse de Rechange Incl</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0BS13X4Z2?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71o8bjO+qpL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0BS13X4Z2</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -7392,11 +7346,11 @@
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="20">
-        <v>1116</v>
+        <v>1067</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG12" s="22">
         <v>0</v>
@@ -7448,7 +7402,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0C3VKT151</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -7461,23 +7415,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig Nettoyeur Détacheur TWT77, Shampouineuse, Nettoyeur Tapis Canapé et Tissu, Double Réservoir, Brosse de Rechange Incl</t>
+          <t>SUPER CLEAN Nettoyant concentré tapis et tissus nettoyage en profondeur adapté aux tapis sièges auto canapés contenu 2 x 500</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0C3VKT151?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51BtUWuNe6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0C3VKT151</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -7498,11 +7452,11 @@
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="20">
-        <v>1067</v>
+        <v>466</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG13" s="22">
         <v>0</v>
@@ -7554,7 +7508,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0C3VKT151</t>
+          <t>B0CFRBWJKR</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -7567,23 +7521,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>SUPER CLEAN Nettoyant concentré tapis et tissus nettoyage en profondeur adapté aux tapis sièges auto canapés contenu 2 x 500</t>
+          <t>BISSELL Revolution HydroSteam Nettoyeur Vapeur 1300W 3670NsShampouineuse avec technologie HydroSteam, pour canapé tissu, ta</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0C3VKT151?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CFRBWJKR?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51BtUWuNe6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71b8xKKCoDL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0C3VKT151</t>
+          <t>B0CFRBWJKR</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7599,16 +7553,18 @@
       <c r="W14" s="15"/>
       <c r="X14" s="15"/>
       <c r="Y14"/>
-      <c r="Z14" s="19"/>
+      <c r="Z14" s="19">
+        <v>249.98</v>
+      </c>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="20">
-        <v>466</v>
+        <v>654</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="21">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AG14" s="22">
         <v>0</v>
@@ -7660,7 +7616,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0CFRBWJKR</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -7673,23 +7629,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Revolution HydroSteam Nettoyeur Vapeur 1300W 3670NsShampouineuse avec technologie HydroSteam, pour canapé tissu, ta</t>
+          <t>Lehmann Prowash 2000 Professionnel Aspirateur Nettoyeur, Multifonction Shampouineuse Idéal pour Canapé, Tapis, Rembourrage, V</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CFRBWJKR?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71b8xKKCoDL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/7147V4eSgzL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0CFRBWJKR</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7705,18 +7661,16 @@
       <c r="W15" s="15"/>
       <c r="X15" s="15"/>
       <c r="Y15"/>
-      <c r="Z15" s="19">
-        <v>249.98</v>
-      </c>
+      <c r="Z15" s="19"/>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="20">
-        <v>654</v>
+        <v>385</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG15" s="22">
         <v>0</v>
@@ -7768,7 +7722,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0CN6QV2FC</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -7781,23 +7735,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Lehmann Prowash 2000 Professionnel Aspirateur Nettoyeur, Multifonction Shampouineuse Idéal pour Canapé, Tapis, Rembourrage, V</t>
+          <t>Kärcher Shampouineuse SE 5, Flexible d'Aspiration 2 en 1, Réservoir d'eau Fraîche : 4 l, Réservoir d'eau Sale : 4 l, Suceur S</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CN6QV2FC?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7147V4eSgzL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61iZnWRpCEL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0CN6QV2FC</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7818,11 +7772,11 @@
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="20">
-        <v>385</v>
+        <v>72</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="21">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AG16" s="22">
         <v>0</v>
@@ -7874,7 +7828,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0CN6QV2FC</t>
+          <t>B0CW9VBM8R</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -7887,23 +7841,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Kärcher Shampouineuse SE 5, Flexible d'Aspiration 2 en 1, Réservoir d'eau Fraîche : 4 l, Réservoir d'eau Sale : 4 l, Suceur S</t>
+          <t>BISSELL SpotClean C5 Shampouineuse Canapé 400W 3861NsNettoyeur léger avec système Triple Action, pour tapis, moquettes, meu</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CN6QV2FC?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CW9VBM8R?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61iZnWRpCEL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71aulycsVkL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0CN6QV2FC</t>
+          <t>B0CW9VBM8R</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7919,16 +7873,18 @@
       <c r="W17" s="15"/>
       <c r="X17" s="15"/>
       <c r="Y17"/>
-      <c r="Z17" s="19"/>
+      <c r="Z17" s="19">
+        <v>124.99</v>
+      </c>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="20">
-        <v>72</v>
+        <v>4637</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="21">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AG17" s="22">
         <v>0</v>
@@ -7980,7 +7936,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0CW9VBM8R</t>
+          <t>B0CXJLJQD1</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -7993,23 +7949,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean C5 Shampouineuse Canapé 400W 3861NsNettoyeur léger avec système Triple Action, pour tapis, moquettes, meu</t>
+          <t>BISSELL SpotClean ProHeat Advanced Shampouineuse Canapé 1125W 3924NsCompacte multi-surfaces, triple nettoyage pour taches t</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CW9VBM8R?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CXJLJQD1?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71aulycsVkL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6194eCgEtDL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0CW9VBM8R</t>
+          <t>B0CXJLJQD1</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8026,17 +7982,17 @@
       <c r="X18" s="15"/>
       <c r="Y18"/>
       <c r="Z18" s="19">
-        <v>124.99</v>
+        <v>166.66</v>
       </c>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="20">
-        <v>4637</v>
+        <v>710</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG18" s="22">
         <v>0</v>
@@ -8088,7 +8044,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0CXJLJQD1</t>
+          <t>B0D2LPJ59Q</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8101,23 +8057,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean ProHeat Advanced Shampouineuse Canapé 1125W 3924NsCompacte multi-surfaces, triple nettoyage pour taches t</t>
+          <t>Shark StainStriker Nettoyeur tâches 5 accessoires, pour animaux, suceur plat et tuyaux, 2 formules de nettoyage CarpetXpert (</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CXJLJQD1?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0D2LPJ59Q?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6194eCgEtDL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/719iSHm2ywL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0CXJLJQD1</t>
+          <t>B0D2LPJ59Q</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8134,13 +8090,13 @@
       <c r="X19" s="15"/>
       <c r="Y19"/>
       <c r="Z19" s="19">
-        <v>166.66</v>
+        <v>156.34</v>
       </c>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="20">
-        <v>710</v>
+        <v>741</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="21">
@@ -8196,7 +8152,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0D2LPJ59Q</t>
+          <t>B0DD49JNRL</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8209,23 +8165,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker Nettoyeur tâches 5 accessoires, pour animaux, suceur plat et tuyaux, 2 formules de nettoyage CarpetXpert (</t>
+          <t>Rowenta - Clean It Shampouineuse Détacheur de Taches et - Bleu - NoirsNettoyage tapis et tissus par pulvérisation - Frottem</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0D2LPJ59Q?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0DD49JNRL?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/719iSHm2ywL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81XkUen8OfL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0D2LPJ59Q</t>
+          <t>B0DD49JNRL</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8242,13 +8198,13 @@
       <c r="X20" s="15"/>
       <c r="Y20"/>
       <c r="Z20" s="19">
-        <v>156.34</v>
+        <v>116.66</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="20">
-        <v>741</v>
+        <v>1712</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="21">
@@ -8304,7 +8260,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0DD49JNRL</t>
+          <t>B0DFLYY2H7</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8317,23 +8273,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Rowenta - Clean It Shampouineuse Détacheur de Taches et - Bleu - NoirsNettoyage tapis et tissus par pulvérisation - Frottem</t>
+          <t>Vacmaster Aspirateur Balai Nettoyeurs tapis et moquettes Lave et Élimine la Saleté, les Taches Difficiles et Collantes Pour T</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DD49JNRL?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0DFLYY2H7?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81XkUen8OfL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/7154Sj-lWDL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0DD49JNRL</t>
+          <t>B0DFLYY2H7</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8350,13 +8306,13 @@
       <c r="X21" s="15"/>
       <c r="Y21"/>
       <c r="Z21" s="19">
-        <v>116.66</v>
+        <v>166.66</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="20">
-        <v>1712</v>
+        <v>256</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="21">
@@ -8412,7 +8368,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0DFLYY2H7</t>
+          <t>B0DN68M1FK</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8425,23 +8381,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Aspirateur Balai Nettoyeurs tapis et moquettes Lave et Élimine la Saleté, les Taches Difficiles et Collantes Pour T</t>
+          <t>BISSELL PowerWash Compact Pet Shampouineuse Multisurfaces 600W 4058NsPour taches et odeurs d'animaux, nettoyeur canapé tiss</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DFLYY2H7?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0DN68M1FK?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7154Sj-lWDL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/617VZB4pynL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0DFLYY2H7</t>
+          <t>B0DN68M1FK</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8458,17 +8414,17 @@
       <c r="X22" s="15"/>
       <c r="Y22"/>
       <c r="Z22" s="19">
-        <v>166.66</v>
+        <v>149.99</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="20">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -8520,7 +8476,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0DN68M1FK</t>
+          <t>B0DNJGVFH8</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8533,23 +8489,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>BISSELL PowerWash Compact Pet Shampouineuse Multisurfaces 600W 4058NsPour taches et odeurs d'animaux, nettoyeur canapé tiss</t>
+          <t>Vacmaster SCC1201H Shampouineuse Canapé, Moteur Puissant de 500W, Nettoyeurs tapis et moquettes Idéal pour Taches &amp; Saletés Q</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DN68M1FK?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0DNJGVFH8?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/617VZB4pynL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pN17PPglL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0DN68M1FK</t>
+          <t>B0DNJGVFH8</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8566,17 +8522,17 @@
       <c r="X23" s="15"/>
       <c r="Y23"/>
       <c r="Z23" s="19">
-        <v>149.99</v>
+        <v>62.59</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="20">
-        <v>208</v>
+        <v>510</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -8628,7 +8584,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0DNJGVFH8</t>
+          <t>B0F4SZVPP9</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8641,23 +8597,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster SCC1201H Shampouineuse Canapé, Moteur Puissant de 500W, Nettoyeurs tapis et moquettes Idéal pour Taches &amp; Saletés Q</t>
+          <t>DUSTGO - Shampouineuse Canapé Tissu, Nettoyeur pour Tapis &amp; Moquettes, Moteur 600W Compact, Nettoyeur Voiture, Réservoir Amov</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DNJGVFH8?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F4SZVPP9?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pN17PPglL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51IrizbrWoL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0DNJGVFH8</t>
+          <t>B0F4SZVPP9</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8673,14 +8629,12 @@
       <c r="W24" s="15"/>
       <c r="X24" s="15"/>
       <c r="Y24"/>
-      <c r="Z24" s="19">
-        <v>62.59</v>
-      </c>
+      <c r="Z24" s="19"/>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="20">
-        <v>510</v>
+        <v>312</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="21">
@@ -8736,7 +8690,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0F4SZVPP9</t>
+          <t>B0F6CWS4ZN</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8749,23 +8703,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>DUSTGO - Shampouineuse Canapé Tissu, Nettoyeur pour Tapis &amp; Moquettes, Moteur 600W Compact, Nettoyeur Voiture, Réservoir Amov</t>
+          <t>BISSELL SpotClean Mini Shampouineuse Filaire 41491sNettoyeur tapis portable, idéal pour nettoyages rapides, compact et lége</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F4SZVPP9?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F6CWS4ZN?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51IrizbrWoL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61EH58S55TL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0F4SZVPP9</t>
+          <t>B0F6CWS4ZN</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8781,16 +8735,18 @@
       <c r="W25" s="15"/>
       <c r="X25" s="15"/>
       <c r="Y25"/>
-      <c r="Z25" s="19"/>
+      <c r="Z25" s="19">
+        <v>74.99</v>
+      </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="20">
-        <v>312</v>
+        <v>727</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -8842,7 +8798,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0F6CWS4ZN</t>
+          <t>B0FD9R33PF</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8855,23 +8811,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean Mini Shampouineuse Filaire 41491sNettoyeur tapis portable, idéal pour nettoyages rapides, compact et lége</t>
+          <t>Welsauber Shampouineuse Canapé et Tapis 600W, Nettoyeur Textile 18 kPa avec Aspiration Puissante, Injecteur Extracteur pour C</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F6CWS4ZN?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FD9R33PF?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61EH58S55TL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/715cAyIFD7L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0F6CWS4ZN</t>
+          <t>B0FD9R33PF</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8887,18 +8843,16 @@
       <c r="W26" s="15"/>
       <c r="X26" s="15"/>
       <c r="Y26"/>
-      <c r="Z26" s="19">
-        <v>74.99</v>
-      </c>
+      <c r="Z26" s="19"/>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="20">
-        <v>727</v>
+        <v>355</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -8950,7 +8904,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FD9R33PF</t>
+          <t>B0FFHS6LWS</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8963,23 +8917,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Welsauber Shampouineuse Canapé et Tapis 600W, Nettoyeur Textile 18 kPa avec Aspiration Puissante, Injecteur Extracteur pour C</t>
+          <t>Olvy Aspirateur Balai sans Fil Puissant Cycloniques1 Appareil | 35000 Pa 350W Ecran LED Touch | Sol Dur &amp; Tapis | Aspirateu</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FD9R33PF?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FFHS6LWS?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/715cAyIFD7L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/716YXwXkd-L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FD9R33PF</t>
+          <t>B0FFHS6LWS</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -9000,11 +8954,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="20">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -9056,7 +9010,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FFHS6LWS</t>
+          <t>B0FFJ3KJJT</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9069,23 +9023,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Olvy Aspirateur Balai sans Fil Puissant Cycloniques1 Appareil | 35000 Pa 350W Ecran LED Touch | Sol Dur &amp; Tapis | Aspirateu</t>
+          <t>Olvy Shampouineuse Canape Nettoyeur Tapis Injecteur Extracteurs1 Appareil | 1650W Vapeur 100C 13000 PA | Siege Auto &amp; Matel</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FFHS6LWS?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FFJ3KJJT?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/716YXwXkd-L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FFHS6LWS</t>
+          <t>B0FFJ3KJJT</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9106,11 +9060,11 @@
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="20">
-        <v>316</v>
+        <v>1481</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -9162,7 +9116,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FFJ3KJJT</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9175,23 +9129,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Olvy Shampouineuse Canape Nettoyeur Tapis Injecteur Extracteurs1 Appareil | 1650W Vapeur 100C 13000 PA | Siege Auto &amp; Matel</t>
+          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et TapissEau propre 2,3 L, eau sale 1,3 L pour nettoyer plus</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FFJ3KJJT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FFJ3KJJT</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9212,7 +9166,7 @@
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="20">
-        <v>1481</v>
+        <v>326</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="21">
@@ -9268,7 +9222,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9281,23 +9235,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et TapissEau propre 2,3 L, eau sale 1,3 L pour nettoyer plus</t>
+          <t>Akitas X7 600W Shampouineuse Canapé avec Fonction Autonettoyante, Aspiration 14kPa, Poils d’Animaux, Nettoyeur Tapis, Matelas</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FJFDG5PY?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9318,7 +9272,7 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="20">
-        <v>326</v>
+        <v>2778</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="21">
@@ -9374,7 +9328,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0FJFQLDTZ</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9387,23 +9341,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Akitas X7 600W Shampouineuse Canapé avec Fonction Autonettoyante, Aspiration 14kPa, Poils d’Animaux, Nettoyeur Tapis, Matelas</t>
+          <t>Rowenta - Shampouineuse Clean It Compact Détacheur Portable GrisesNettoyage tapis - Canapés et voiture - Élimine taches d'a</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FJFDG5PY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FJFQLDTZ?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71nqcfMen+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0FJFQLDTZ</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9419,16 +9373,18 @@
       <c r="W31" s="15"/>
       <c r="X31" s="15"/>
       <c r="Y31"/>
-      <c r="Z31" s="19"/>
+      <c r="Z31" s="19">
+        <v>74.99</v>
+      </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="20">
-        <v>2778</v>
+        <v>427</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -9480,7 +9436,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0FJFQLDTZ</t>
+          <t>B0FKSTVY4B</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9493,23 +9449,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Rowenta - Shampouineuse Clean It Compact Détacheur Portable GrisesNettoyage tapis - Canapés et voiture - Élimine taches d'a</t>
+          <t>Livatro Shampouineuse à Vapeur 100 °C pour Canapés et Tissuss1700 W, vapeur prête en 30 s pour aider à décoller les résidus</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FJFQLDTZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FKSTVY4B?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71nqcfMen+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61vNLxoQL3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0FJFQLDTZ</t>
+          <t>B0FKSTVY4B</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9525,18 +9481,16 @@
       <c r="W32" s="15"/>
       <c r="X32" s="15"/>
       <c r="Y32"/>
-      <c r="Z32" s="19">
-        <v>74.99</v>
-      </c>
+      <c r="Z32" s="19"/>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="20">
-        <v>427</v>
+        <v>223</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="21">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
@@ -9588,7 +9542,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0FKSTVY4B</t>
+          <t>B0FL7GZKJW</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9601,23 +9555,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Livatro Shampouineuse à Vapeur 100 °C pour Canapés et Tissuss1700 W, vapeur prête en 30 s pour aider à décoller les résidus</t>
+          <t>Cecotec Nettoyeur Aspirateur de Tapisseries et Moquettes avec Câble Compact Conga 3000 Carpet&amp;Spot Clean X-Treme. 450W, 13kPa</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FKSTVY4B?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FL7GZKJW?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61vNLxoQL3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71J-puz9iAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0FKSTVY4B</t>
+          <t>B0FL7GZKJW</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9638,11 +9592,11 @@
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="20">
-        <v>223</v>
+        <v>87</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="21">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
@@ -9694,7 +9648,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0FL7GZKJW</t>
+          <t>B0FPGHCD96</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9707,23 +9661,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Nettoyeur Aspirateur de Tapisseries et Moquettes avec Câble Compact Conga 3000 Carpet&amp;Spot Clean X-Treme. 450W, 13kPa</t>
+          <t>Kärcher Détacheur SE 2 Spot Care, puissance d'absorption : 450 W, réservoir d’eau propre: 1,5 l, surface : 2,89 m², poids: 4,</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FL7GZKJW?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FPGHCD96?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71J-puz9iAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0FL7GZKJW</t>
+          <t>B0FPGHCD96</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9739,16 +9693,18 @@
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
       <c r="Y34"/>
-      <c r="Z34" s="19"/>
+      <c r="Z34" s="19">
+        <v>99.99</v>
+      </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="20">
-        <v>87</v>
+        <v>519</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
@@ -9800,7 +9756,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0FPGHCD96</t>
+          <t>B0FPMM29LT</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9813,23 +9769,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Kärcher Détacheur SE 2 Spot Care, puissance d'absorption : 450 W, réservoir d’eau propre: 1,5 l, surface : 2,89 m², poids: 4,</t>
+          <t>Shark StainStriker HairPro spécial animaux, Aspiration 450 W PX250EUCPsExtracteur de poils, Élimine taches et odeurs, Léger</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FPGHCD96?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FPMM29LT?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71WUwhk+oAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0FPGHCD96</t>
+          <t>B0FPMM29LT</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9846,17 +9802,17 @@
       <c r="X35" s="15"/>
       <c r="Y35"/>
       <c r="Z35" s="19">
-        <v>99.99</v>
+        <v>149.99</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="20">
-        <v>519</v>
+        <v>99</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
@@ -9908,7 +9864,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0FPMM29LT</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9921,23 +9877,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker HairPro spécial animaux, Aspiration 450 W PX250EUCPsExtracteur de poils, Élimine taches et odeurs, Léger</t>
+          <t>ICARE Shampouineuse 600w - 15kPa Nettoyeur Canapé Tissu - Avec DétergentsDétacheur Nettoyeur de Tache - Shampouineuse Canap</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FPMM29LT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0G8ZCQP4L?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71WUwhk+oAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71of0gNYa6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0FPMM29LT</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9953,18 +9909,16 @@
       <c r="W36" s="15"/>
       <c r="X36" s="15"/>
       <c r="Y36"/>
-      <c r="Z36" s="19">
-        <v>149.99</v>
-      </c>
+      <c r="Z36" s="19"/>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="20">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="21">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AG36" s="22">
         <v>0</v>
@@ -10016,7 +9970,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0G8ZCQP4L</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10029,23 +9983,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>ICARE Shampouineuse 600w - 15kPa Nettoyeur Canapé Tissu - Avec DétergentsDétacheur Nettoyeur de Tache - Shampouineuse Canap</t>
+          <t>Akitas X5 Shampouineuse Canapé avec Fonction Autonettoyante, Inclus : 30ml Solution Concentrée de Démarrage Idéal pour Poils</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0G8ZCQP4L?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GFF7C519?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71of0gNYa6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71lXldTzTtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0G8ZCQP4L</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10066,11 +10020,11 @@
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="20">
-        <v>12</v>
+        <v>244</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="21">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AG37" s="22">
         <v>0</v>
@@ -10122,7 +10076,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0GFKK2WXT</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10135,23 +10089,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Akitas X5 Shampouineuse Canapé avec Fonction Autonettoyante, Inclus : 30ml Solution Concentrée de Démarrage Idéal pour Poils</t>
+          <t>Vacmaster Nettoyeur tapis chauffant 1150W 17KPA auto-nettoyage canapésauto-nettoyage Aspirateur Nettoyeur à Vapeur 50°C Net</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GFF7C519?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GFKK2WXT?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71lXldTzTtL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0GFKK2WXT</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10167,16 +10121,18 @@
       <c r="W38" s="15"/>
       <c r="X38" s="15"/>
       <c r="Y38"/>
-      <c r="Z38" s="19"/>
+      <c r="Z38" s="19">
+        <v>74.99</v>
+      </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="20">
-        <v>244</v>
+        <v>25</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG38" s="22">
         <v>0</v>
@@ -10228,7 +10184,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GFKK2WXT</t>
+          <t>B0GH6TBJVW</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10241,23 +10197,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Nettoyeur tapis chauffant 1150W 17KPA auto-nettoyage canapésauto-nettoyage Aspirateur Nettoyeur à Vapeur 50°C Net</t>
+          <t>Kitcanis Nettoyeur Canapé Tissu 17000Pa - 78dB 600W Shampouineuse Canape avec 4 Buses Fonction d’Auto-Nettoyage Aspirateur po</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GFKK2WXT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GH6TBJVW?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71j7k36yP8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GFKK2WXT</t>
+          <t>B0GH6TBJVW</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10273,18 +10229,16 @@
       <c r="W39" s="15"/>
       <c r="X39" s="15"/>
       <c r="Y39"/>
-      <c r="Z39" s="19">
-        <v>74.99</v>
-      </c>
+      <c r="Z39" s="19"/>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="20">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG39" s="22">
         <v>0</v>
@@ -10336,7 +10290,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GH6TBJVW</t>
+          <t>B0GHQBM3W1</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10349,23 +10303,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Kitcanis Nettoyeur Canapé Tissu 17000Pa - 78dB 600W Shampouineuse Canape avec 4 Buses Fonction d’Auto-Nettoyage Aspirateur po</t>
+          <t>SIMPLUS Shampouineuse Canapé avec Fonction Autonettoyante, Nettoyeur Tissus Puissant 12000Pa, Idéal pour Poils d’Animaux, Net</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GH6TBJVW?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GHQBM3W1?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71j7k36yP8L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71U+g7bkr+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GH6TBJVW</t>
+          <t>B0GHQBM3W1</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10386,11 +10340,11 @@
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="20">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG40" s="22">
         <v>0</v>
@@ -10442,7 +10396,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0GHQBM3W1</t>
+          <t>B0GHQWRZLV</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10455,23 +10409,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS Shampouineuse Canapé avec Fonction Autonettoyante, Nettoyeur Tissus Puissant 12000Pa, Idéal pour Poils d’Animaux, Net</t>
+          <t>SIMPLUS Nettoyeur Vapeur Tissu Canapé Portable avec Fonction Eau Chaude 110℃, Shampouineuse Extracteur 22000Pa, Double Réserv</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GHQBM3W1?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GHQWRZLV?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71U+g7bkr+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71LN+xCoF4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0GHQBM3W1</t>
+          <t>B0GHQWRZLV</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10492,11 +10446,11 @@
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="20">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG41" s="22">
         <v>0</v>
@@ -10548,7 +10502,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0GHQWRZLV</t>
+          <t>B0GK9FV3ZM</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10561,23 +10515,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS Nettoyeur Vapeur Tissu Canapé Portable avec Fonction Eau Chaude 110℃, Shampouineuse Extracteur 22000Pa, Double Réserv</t>
+          <t>BISSELL Little Green Mini, détacheur portable, puissance et portabilité inégalées, nettoyage multi-surfaces, léger, portable,</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GHQWRZLV?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GK9FV3ZM?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71LN+xCoF4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6127eJoRLkL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0GHQWRZLV</t>
+          <t>B0GK9FV3ZM</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10593,16 +10547,18 @@
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
       <c r="Y42"/>
-      <c r="Z42" s="19"/>
+      <c r="Z42" s="19">
+        <v>83.32</v>
+      </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="20">
-        <v>24</v>
+        <v>93072</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG42" s="22">
         <v>0</v>
@@ -10654,7 +10610,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0GK9FV3ZM</t>
+          <t>B0GQ3FT1J1</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10667,23 +10623,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Mini, détacheur portable, puissance et portabilité inégalées, nettoyage multi-surfaces, léger, portable,</t>
+          <t>Lubluelu Shampouineuse Canapé 600 W, 22 kPa, Nettoyeur Tapis PortablesAuto-Nettoyante et Portable, avec Long Tuyau pour Can</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GK9FV3ZM?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GQ3FT1J1?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6127eJoRLkL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71N7QTjqAWL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0GK9FV3ZM</t>
+          <t>B0GQ3FT1J1</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10699,18 +10655,16 @@
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
       <c r="Y43"/>
-      <c r="Z43" s="19">
-        <v>83.32</v>
-      </c>
+      <c r="Z43" s="19"/>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="20">
-        <v>93072</v>
+        <v>16</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="21">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AG43" s="22">
         <v>0</v>
@@ -10762,7 +10716,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0GQ3FT1J1</t>
+          <t>B0GQVHQNNV</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10775,23 +10729,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Shampouineuse Canapé 600 W, 22 kPa, Nettoyeur Tapis PortablesAuto-Nettoyante et Portable, avec Long Tuyau pour Can</t>
+          <t>Rowenta - Shampouineuse Clean It Hot &amp; Cold Orange et - 1150w - NoirsNettoyeur tapis et canapé avec technologie PowerHeat 6</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GQ3FT1J1?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GQVHQNNV?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71N7QTjqAWL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71X4xzZtzYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0GQ3FT1J1</t>
+          <t>B0GQVHQNNV</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10807,16 +10761,18 @@
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
       <c r="Y44"/>
-      <c r="Z44" s="19"/>
+      <c r="Z44" s="19">
+        <v>208.32</v>
+      </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="20">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="21">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG44" s="22">
         <v>0</v>
@@ -10868,7 +10824,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0GQVHQNNV</t>
+          <t>B0GTQ7NRR5</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10881,23 +10837,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Rowenta - Shampouineuse Clean It Hot &amp; Cold Orange et - 1150w - NoirsNettoyeur tapis et canapé avec technologie PowerHeat 6</t>
+          <t>Redkey C2 Shampouineuse, 1800W 26000Pa Nettoyeur Canapé Tissu, Nettoyeur Vapeur 4-en-1 Aspirateur Eau et Poussière pour Canap</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GQVHQNNV?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GTQ7NRR5?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71X4xzZtzYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/710LGMIAr9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0GQVHQNNV</t>
+          <t>B0GTQ7NRR5</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10914,17 +10870,17 @@
       <c r="X45" s="15"/>
       <c r="Y45"/>
       <c r="Z45" s="19">
-        <v>208.32</v>
+        <v>110.82</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="20">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG45" s="22">
         <v>0</v>
@@ -10976,7 +10932,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0GTQ7NRR5</t>
+          <t>B0GZVZYBP4</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -10989,23 +10945,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Redkey C2 Shampouineuse, 1800W 26000Pa Nettoyeur Canapé Tissu, Nettoyeur Vapeur 4-en-1 Aspirateur Eau et Poussière pour Canap</t>
+          <t>SIMPLUS Shampouineuse à Vapeur 100 °C pour Canapés et Tissus, Blancs18 kPa, 1650W, Injecteur Extracteur Portable, avec Doub</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GTQ7NRR5?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GZVZYBP4?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/710LGMIAr9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71FX9pIta2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0GTQ7NRR5</t>
+          <t>B0GZVZYBP4</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -11021,18 +10977,16 @@
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
       <c r="Y46"/>
-      <c r="Z46" s="19">
-        <v>110.82</v>
-      </c>
+      <c r="Z46" s="19"/>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="20">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="21">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG46" s="22">
         <v>0</v>
@@ -11084,7 +11038,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0GZVZYBP4</t>
+          <t>B0H1B164KH</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11097,23 +11051,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS Shampouineuse à Vapeur 100 °C pour Canapés et Tissus, Blancs18 kPa, 1650W, Injecteur Extracteur Portable, avec Doub</t>
+          <t>Uwant Y100S 3-en-1 Shampouineuse, Nettoyeur Canapé Tissu pour Canape/Tapiss18 kPa,1750W,Tuyau Autonettoyant,Multiples Bross</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GZVZYBP4?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H1B164KH?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71FX9pIta2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71fqxg6JLpL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0GZVZYBP4</t>
+          <t>B0H1B164KH</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11134,11 +11088,11 @@
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="20">
-        <v>12</v>
+        <v>335</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="21">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
@@ -11190,7 +11144,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H1B164KH</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11203,23 +11157,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Uwant Y100S 3-en-1 Shampouineuse, Nettoyeur Canapé Tissu pour Canape/Tapiss18 kPa,1750W,Tuyau Autonettoyant,Multiples Bross</t>
+          <t>LEHMANN SteamWash 1800 - Nettoyeur Vapeur 4 en 1 &amp; Aspirateur Injecteur Extracteur, Nettoyeur à Main Portable Canapé, Tapis,</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H1B164KH?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H3LCDNGF?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71fqxg6JLpL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H1B164KH</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11240,11 +11194,11 @@
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="20">
-        <v>335</v>
+        <v>28</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
@@ -11296,7 +11250,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0H8RB6DK4</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11309,23 +11263,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN SteamWash 1800 - Nettoyeur Vapeur 4 en 1 &amp; Aspirateur Injecteur Extracteur, Nettoyeur à Main Portable Canapé, Tapis,</t>
+          <t>Aspirateur à Eau Pour Tissus D'ameublement, Nettoyant HumidesCanapés, tapis et matelas| Moteur 500W, aspiration 18 kPa | Pi</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H3LCDNGF?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H8RB6DK4?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61iNA78DGuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0H8RB6DK4</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11346,11 +11300,11 @@
       <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49" s="20">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AE49"/>
       <c r="AF49" s="21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG49" s="22">
         <v>0</v>
@@ -11402,7 +11356,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0H8RB6DK4</t>
+          <t>B0HBW8TLYC</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -11415,23 +11369,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur à Eau Pour Tissus D'ameublement, Nettoyant HumidesCanapés, tapis et matelas| Moteur 500W, aspiration 18 kPa | Pi</t>
+          <t>Uwant B300PRO Nettoyeur Shampouineuse Canape Professionnel,Aspiration Puissante 18Kpa，Portable avec Accessoires,Nettoyeur Can</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H8RB6DK4?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HBW8TLYC?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61iNA78DGuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71-eDHZgLSL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0H8RB6DK4</t>
+          <t>B0HBW8TLYC</t>
         </is>
       </c>
       <c r="M50" s="1"/>
@@ -11452,11 +11406,11 @@
       <c r="AB50"/>
       <c r="AC50"/>
       <c r="AD50" s="20">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="AE50"/>
       <c r="AF50" s="21">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AG50" s="22">
         <v>0</v>
@@ -11501,112 +11455,6 @@
       <c r="BQ50" s="23"/>
       <c r="BR50"/>
     </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HBW8TLYC</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.frundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Uwant B300PRO Nettoyeur Shampouineuse Canape Professionnel,Aspiration Puissante 18Kpa，Portable avec Accessoires,Nettoyeur Can</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0HBW8TLYC?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71-eDHZgLSL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HBW8TLYC</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="19"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="20">
-        <v>52</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="20"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="20"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -11621,248 +11469,243 @@
     <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
     <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
+    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.fr/dp/B07GXS35PG"/>
     <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.fr/dp/B07999DC2C?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61aI3+gXJwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.fr/dp/B07GXS35PG"/>
+    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.fr/dp/B07GXS35PG?psc=1"/>
+    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/712YG8KRpfL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.fr/dp/B07GXS35PG"/>
+    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.fr/dp/B07NH2DYTN"/>
     <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.fr/dp/B07GXS35PG?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/712YG8KRpfL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.fr/dp/B07GXS35PG"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.fr/dp/B07NH2DYTN"/>
+    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.fr/dp/B07NH2DYTN?psc=1"/>
+    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61uBPKfdYRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.fr/dp/B07NH2DYTN"/>
+    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.fr/dp/B084PSXMQM"/>
     <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.fr/dp/B07NH2DYTN?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61uBPKfdYRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.fr/dp/B07NH2DYTN"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.fr/dp/B084PSXMQM"/>
+    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.fr/dp/B084PSXMQM?psc=1"/>
+    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/717n80vcVUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.fr/dp/B084PSXMQM"/>
+    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.fr/dp/B08DG69QHL"/>
     <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.fr/dp/B084PSXMQM?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/717n80vcVUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.fr/dp/B084PSXMQM"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.fr/dp/B08DG69QHL"/>
+    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.fr/dp/B08DG69QHL?psc=1"/>
+    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41HEOK25hnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.fr/dp/B08DG69QHL"/>
+    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
     <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.fr/dp/B08DG69QHL?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41HEOK25hnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.fr/dp/B08DG69QHL"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
+    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.fr/dp/B08KXVXC82?psc=1"/>
+    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
+    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
     <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.fr/dp/B08KXVXC82?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
+    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.fr/dp/B0BMF3LFC8"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.fr/dp/B0BMF3LFC8"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.fr/dp/B0BMF3LFC8?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.fr/dp/B0BMF3LFC8"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.fr/dp/B0BS13X4Z2"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.fr/dp/B0BMF3LFC8?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.fr/dp/B0BMF3LFC8"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.fr/dp/B0BS13X4Z2"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.fr/dp/B0BS13X4Z2?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71o8bjO+qpL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.fr/dp/B0BS13X4Z2"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.fr/dp/B0BS13X4Z2?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71o8bjO+qpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.fr/dp/B0BS13X4Z2"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.fr/dp/B0C3VKT151?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51BtUWuNe6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.fr/dp/B0CFRBWJKR"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.fr/dp/B0C3VKT151?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51BtUWuNe6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.fr/dp/B0CFRBWJKR"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.fr/dp/B0CFRBWJKR?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71b8xKKCoDL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.fr/dp/B0CFRBWJKR"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.fr/dp/B0CFRBWJKR?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71b8xKKCoDL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.fr/dp/B0CFRBWJKR"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7147V4eSgzL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.fr/dp/B0CN6QV2FC"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7147V4eSgzL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.fr/dp/B0CN6QV2FC"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.fr/dp/B0CN6QV2FC?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61iZnWRpCEL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.fr/dp/B0CN6QV2FC"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.fr/dp/B0CW9VBM8R"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.fr/dp/B0CN6QV2FC?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61iZnWRpCEL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.fr/dp/B0CN6QV2FC"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.fr/dp/B0CW9VBM8R"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.fr/dp/B0CW9VBM8R?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71aulycsVkL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.fr/dp/B0CW9VBM8R"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.fr/dp/B0CXJLJQD1"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.fr/dp/B0CW9VBM8R?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71aulycsVkL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.fr/dp/B0CW9VBM8R"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.fr/dp/B0CXJLJQD1"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.fr/dp/B0CXJLJQD1?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6194eCgEtDL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.fr/dp/B0CXJLJQD1"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.fr/dp/B0D2LPJ59Q"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.fr/dp/B0CXJLJQD1?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6194eCgEtDL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.fr/dp/B0CXJLJQD1"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.fr/dp/B0D2LPJ59Q"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.fr/dp/B0D2LPJ59Q?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719iSHm2ywL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.fr/dp/B0D2LPJ59Q"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.fr/dp/B0DD49JNRL"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.fr/dp/B0D2LPJ59Q?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719iSHm2ywL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.fr/dp/B0D2LPJ59Q"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.fr/dp/B0DD49JNRL"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.fr/dp/B0DD49JNRL?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81XkUen8OfL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.fr/dp/B0DD49JNRL"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.fr/dp/B0DFLYY2H7"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.fr/dp/B0DD49JNRL?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81XkUen8OfL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.fr/dp/B0DD49JNRL"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.fr/dp/B0DFLYY2H7"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.fr/dp/B0DFLYY2H7?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7154Sj-lWDL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.fr/dp/B0DFLYY2H7"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.fr/dp/B0DN68M1FK"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.fr/dp/B0DFLYY2H7?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7154Sj-lWDL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.fr/dp/B0DFLYY2H7"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.fr/dp/B0DN68M1FK"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.fr/dp/B0DN68M1FK?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/617VZB4pynL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.fr/dp/B0DN68M1FK"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.fr/dp/B0DNJGVFH8"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.fr/dp/B0DN68M1FK?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/617VZB4pynL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.fr/dp/B0DN68M1FK"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.fr/dp/B0DNJGVFH8"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.fr/dp/B0DNJGVFH8?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pN17PPglL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.fr/dp/B0DNJGVFH8"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.fr/dp/B0F4SZVPP9"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.fr/dp/B0DNJGVFH8?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pN17PPglL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.fr/dp/B0DNJGVFH8"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.fr/dp/B0F4SZVPP9"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.fr/dp/B0F4SZVPP9?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51IrizbrWoL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.fr/dp/B0F4SZVPP9"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.fr/dp/B0F6CWS4ZN"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.fr/dp/B0F4SZVPP9?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51IrizbrWoL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.fr/dp/B0F4SZVPP9"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.fr/dp/B0F6CWS4ZN"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.fr/dp/B0F6CWS4ZN?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61EH58S55TL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.fr/dp/B0F6CWS4ZN"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.fr/dp/B0FD9R33PF"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.fr/dp/B0F6CWS4ZN?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61EH58S55TL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.fr/dp/B0F6CWS4ZN"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.fr/dp/B0FD9R33PF"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.fr/dp/B0FD9R33PF?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/715cAyIFD7L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.fr/dp/B0FD9R33PF"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.fr/dp/B0FD9R33PF?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/715cAyIFD7L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.fr/dp/B0FD9R33PF"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/716YXwXkd-L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.fr/dp/B0FFJ3KJJT"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/716YXwXkd-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.fr/dp/B0FFJ3KJJT"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.fr/dp/B0FFJ3KJJT?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.fr/dp/B0FFJ3KJJT"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.fr/dp/B0FFJ3KJJT?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.fr/dp/B0FFJ3KJJT"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.fr/dp/B0FJFDG5PY"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.fr/dp/B0FJFDG5PY"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.fr/dp/B0FJFDG5PY?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.fr/dp/B0FJFDG5PY"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.fr/dp/B0FJFQLDTZ"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.fr/dp/B0FJFDG5PY?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.fr/dp/B0FJFDG5PY"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.fr/dp/B0FJFQLDTZ"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.fr/dp/B0FJFQLDTZ?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nqcfMen+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.fr/dp/B0FJFQLDTZ"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.fr/dp/B0FKSTVY4B"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.fr/dp/B0FJFQLDTZ?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nqcfMen+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.fr/dp/B0FJFQLDTZ"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.fr/dp/B0FKSTVY4B"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.fr/dp/B0FKSTVY4B?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61vNLxoQL3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.fr/dp/B0FKSTVY4B"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.fr/dp/B0FL7GZKJW"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.fr/dp/B0FKSTVY4B?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61vNLxoQL3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.fr/dp/B0FKSTVY4B"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.fr/dp/B0FL7GZKJW"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.fr/dp/B0FL7GZKJW?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71J-puz9iAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.fr/dp/B0FL7GZKJW"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.fr/dp/B0FPGHCD96"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.fr/dp/B0FL7GZKJW?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71J-puz9iAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.fr/dp/B0FL7GZKJW"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.fr/dp/B0FPGHCD96"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.fr/dp/B0FPGHCD96?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.fr/dp/B0FPGHCD96"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.fr/dp/B0FPMM29LT"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.fr/dp/B0FPGHCD96?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.fr/dp/B0FPGHCD96"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.fr/dp/B0FPMM29LT"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.fr/dp/B0FPMM29LT?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71WUwhk+oAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.fr/dp/B0FPMM29LT"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.fr/dp/B0FPMM29LT?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71WUwhk+oAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.fr/dp/B0FPMM29LT"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71of0gNYa6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.fr/dp/B0GFF7C519"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71of0gNYa6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.fr/dp/B0G8ZCQP4L"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.fr/dp/B0GFF7C519"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.fr/dp/B0GFF7C519?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71lXldTzTtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.fr/dp/B0GFF7C519"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.fr/dp/B0GFF7C519?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71lXldTzTtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0GFF7C519"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.fr/dp/B0GH6TBJVW"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.fr/dp/B0GH6TBJVW"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.fr/dp/B0GH6TBJVW?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71j7k36yP8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.fr/dp/B0GH6TBJVW"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.fr/dp/B0GH6TBJVW?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71j7k36yP8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.fr/dp/B0GH6TBJVW"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71U+g7bkr+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71U+g7bkr+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71LN+xCoF4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.fr/dp/B0GK9FV3ZM"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71LN+xCoF4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.fr/dp/B0GK9FV3ZM"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.fr/dp/B0GK9FV3ZM?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6127eJoRLkL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.fr/dp/B0GK9FV3ZM"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.fr/dp/B0GQ3FT1J1"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.fr/dp/B0GK9FV3ZM?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6127eJoRLkL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.fr/dp/B0GK9FV3ZM"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.fr/dp/B0GQ3FT1J1"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.fr/dp/B0GQ3FT1J1?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71N7QTjqAWL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.fr/dp/B0GQ3FT1J1"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.fr/dp/B0GQVHQNNV"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.fr/dp/B0GQ3FT1J1?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71N7QTjqAWL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.fr/dp/B0GQ3FT1J1"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.fr/dp/B0GQVHQNNV"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.fr/dp/B0GQVHQNNV?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71X4xzZtzYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.fr/dp/B0GQVHQNNV"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.fr/dp/B0GTQ7NRR5"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.fr/dp/B0GQVHQNNV?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71X4xzZtzYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.fr/dp/B0GQVHQNNV"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0GTQ7NRR5"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.fr/dp/B0GTQ7NRR5?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710LGMIAr9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.fr/dp/B0GTQ7NRR5"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0GTQ7NRR5?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710LGMIAr9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.fr/dp/B0GTQ7NRR5"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71FX9pIta2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.fr/dp/B0H1B164KH"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71FX9pIta2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.fr/dp/B0H1B164KH"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.fr/dp/B0H1B164KH?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71fqxg6JLpL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.fr/dp/B0H1B164KH"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.fr/dp/B0H1B164KH?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71fqxg6JLpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.fr/dp/B0H1B164KH"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.fr/dp/B0H8RB6DK4"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.fr/dp/B0H8RB6DK4"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.fr/dp/B0H8RB6DK4?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61iNA78DGuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.fr/dp/B0H8RB6DK4"/>
+    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.fr/dp/B0HBW8TLYC"/>
     <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.fr/dp/B0H8RB6DK4?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61iNA78DGuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0H8RB6DK4"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.fr/dp/B0HBW8TLYC"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.fr/dp/B0HBW8TLYC?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71-eDHZgLSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.fr/dp/B0HBW8TLYC"/>
+    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.fr/dp/B0HBW8TLYC?psc=1"/>
+    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71-eDHZgLSL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0HBW8TLYC"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId246"/>
 </worksheet>
 </file>
 
